--- a/Assets/@Resources/Data/Excel/LevelData.xlsx
+++ b/Assets/@Resources/Data/Excel/LevelData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B303"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>RequiredExp</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>BaseRequiredExp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>다음 레벨까지 필요 경험치</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>원래 필요 경험치(v2 배수 전)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -459,12 +474,18 @@
       <c r="B4" t="n">
         <v>100</v>
       </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2</v>
       </c>
       <c r="B5" t="n">
+        <v>170</v>
+      </c>
+      <c r="C5" t="n">
         <v>120</v>
       </c>
     </row>
@@ -473,6 +494,9 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
+        <v>263</v>
+      </c>
+      <c r="C6" t="n">
         <v>144</v>
       </c>
     </row>
@@ -481,6 +505,9 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
+        <v>386</v>
+      </c>
+      <c r="C7" t="n">
         <v>173</v>
       </c>
     </row>
@@ -489,6 +516,9 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
+        <v>542</v>
+      </c>
+      <c r="C8" t="n">
         <v>207</v>
       </c>
     </row>
@@ -497,6 +527,9 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
+        <v>746</v>
+      </c>
+      <c r="C9" t="n">
         <v>249</v>
       </c>
     </row>
@@ -505,6 +538,9 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C10" t="n">
         <v>299</v>
       </c>
     </row>
@@ -513,6 +549,9 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C11" t="n">
         <v>358</v>
       </c>
     </row>
@@ -521,6 +560,9 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
+        <v>1755</v>
+      </c>
+      <c r="C12" t="n">
         <v>430</v>
       </c>
     </row>
@@ -529,6 +571,9 @@
         <v>10</v>
       </c>
       <c r="B13" t="n">
+        <v>2283</v>
+      </c>
+      <c r="C13" t="n">
         <v>516</v>
       </c>
     </row>
@@ -537,6 +582,9 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
+        <v>2947</v>
+      </c>
+      <c r="C14" t="n">
         <v>619</v>
       </c>
     </row>
@@ -545,6 +593,9 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
+        <v>3780</v>
+      </c>
+      <c r="C15" t="n">
         <v>743</v>
       </c>
     </row>
@@ -553,6 +604,9 @@
         <v>13</v>
       </c>
       <c r="B16" t="n">
+        <v>4822</v>
+      </c>
+      <c r="C16" t="n">
         <v>892</v>
       </c>
     </row>
@@ -561,6 +615,9 @@
         <v>14</v>
       </c>
       <c r="B17" t="n">
+        <v>6117</v>
+      </c>
+      <c r="C17" t="n">
         <v>1070</v>
       </c>
     </row>
@@ -569,6 +626,9 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
+        <v>7730</v>
+      </c>
+      <c r="C18" t="n">
         <v>1284</v>
       </c>
     </row>
@@ -577,6 +637,9 @@
         <v>16</v>
       </c>
       <c r="B19" t="n">
+        <v>9733</v>
+      </c>
+      <c r="C19" t="n">
         <v>1541</v>
       </c>
     </row>
@@ -585,6 +648,9 @@
         <v>17</v>
       </c>
       <c r="B20" t="n">
+        <v>12212</v>
+      </c>
+      <c r="C20" t="n">
         <v>1849</v>
       </c>
     </row>
@@ -593,6 +659,9 @@
         <v>18</v>
       </c>
       <c r="B21" t="n">
+        <v>15280</v>
+      </c>
+      <c r="C21" t="n">
         <v>2219</v>
       </c>
     </row>
@@ -601,6 +670,9 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
+        <v>19061</v>
+      </c>
+      <c r="C22" t="n">
         <v>2662</v>
       </c>
     </row>
@@ -609,6 +681,9 @@
         <v>20</v>
       </c>
       <c r="B23" t="n">
+        <v>23732</v>
+      </c>
+      <c r="C23" t="n">
         <v>3195</v>
       </c>
     </row>
@@ -617,6 +692,9 @@
         <v>21</v>
       </c>
       <c r="B24" t="n">
+        <v>29480</v>
+      </c>
+      <c r="C24" t="n">
         <v>3834</v>
       </c>
     </row>
@@ -625,6 +703,9 @@
         <v>22</v>
       </c>
       <c r="B25" t="n">
+        <v>36548</v>
+      </c>
+      <c r="C25" t="n">
         <v>4601</v>
       </c>
     </row>
@@ -633,6 +714,9 @@
         <v>23</v>
       </c>
       <c r="B26" t="n">
+        <v>45227</v>
+      </c>
+      <c r="C26" t="n">
         <v>5521</v>
       </c>
     </row>
@@ -641,6 +725,9 @@
         <v>24</v>
       </c>
       <c r="B27" t="n">
+        <v>55875</v>
+      </c>
+      <c r="C27" t="n">
         <v>6625</v>
       </c>
     </row>
@@ -649,6 +736,9 @@
         <v>25</v>
       </c>
       <c r="B28" t="n">
+        <v>68928</v>
+      </c>
+      <c r="C28" t="n">
         <v>7950</v>
       </c>
     </row>
@@ -657,6 +747,9 @@
         <v>26</v>
       </c>
       <c r="B29" t="n">
+        <v>84911</v>
+      </c>
+      <c r="C29" t="n">
         <v>9540</v>
       </c>
     </row>
@@ -665,6 +758,9 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
+        <v>104466</v>
+      </c>
+      <c r="C30" t="n">
         <v>11448</v>
       </c>
     </row>
@@ -673,6 +769,9 @@
         <v>28</v>
       </c>
       <c r="B31" t="n">
+        <v>128363</v>
+      </c>
+      <c r="C31" t="n">
         <v>13737</v>
       </c>
     </row>
@@ -681,6 +780,9 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
+        <v>157555</v>
+      </c>
+      <c r="C32" t="n">
         <v>16484</v>
       </c>
     </row>
@@ -689,6 +791,9 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
+        <v>193191</v>
+      </c>
+      <c r="C33" t="n">
         <v>19781</v>
       </c>
     </row>
@@ -697,6 +802,9 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
+        <v>236662</v>
+      </c>
+      <c r="C34" t="n">
         <v>23738</v>
       </c>
     </row>
@@ -705,6 +813,9 @@
         <v>32</v>
       </c>
       <c r="B35" t="n">
+        <v>289636</v>
+      </c>
+      <c r="C35" t="n">
         <v>28485</v>
       </c>
     </row>
@@ -713,6 +824,9 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
+        <v>354174</v>
+      </c>
+      <c r="C36" t="n">
         <v>34182</v>
       </c>
     </row>
@@ -721,6 +835,9 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
+        <v>432751</v>
+      </c>
+      <c r="C37" t="n">
         <v>41019</v>
       </c>
     </row>
@@ -729,6 +846,9 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
+        <v>528346</v>
+      </c>
+      <c r="C38" t="n">
         <v>49222</v>
       </c>
     </row>
@@ -737,6 +857,9 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
+        <v>644619</v>
+      </c>
+      <c r="C39" t="n">
         <v>59067</v>
       </c>
     </row>
@@ -745,6 +868,9 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
+        <v>785940</v>
+      </c>
+      <c r="C40" t="n">
         <v>70880</v>
       </c>
     </row>
@@ -753,6 +879,9 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
+        <v>957643</v>
+      </c>
+      <c r="C41" t="n">
         <v>85056</v>
       </c>
     </row>
@@ -761,6 +890,9 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
+        <v>1166157</v>
+      </c>
+      <c r="C42" t="n">
         <v>102067</v>
       </c>
     </row>
@@ -769,6 +901,9 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
+        <v>1419277</v>
+      </c>
+      <c r="C43" t="n">
         <v>122481</v>
       </c>
     </row>
@@ -777,6 +912,9 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
+        <v>1611311</v>
+      </c>
+      <c r="C44" t="n">
         <v>137179</v>
       </c>
     </row>
@@ -785,6 +923,9 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
+        <v>1828387</v>
+      </c>
+      <c r="C45" t="n">
         <v>153640</v>
       </c>
     </row>
@@ -793,6 +934,9 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
+        <v>2073710</v>
+      </c>
+      <c r="C46" t="n">
         <v>172077</v>
       </c>
     </row>
@@ -801,6 +945,9 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
+        <v>2350860</v>
+      </c>
+      <c r="C47" t="n">
         <v>192726</v>
       </c>
     </row>
@@ -809,6 +956,9 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
+        <v>2663883</v>
+      </c>
+      <c r="C48" t="n">
         <v>215853</v>
       </c>
     </row>
@@ -817,6 +967,9 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
+        <v>3017334</v>
+      </c>
+      <c r="C49" t="n">
         <v>241756</v>
       </c>
     </row>
@@ -825,6 +978,9 @@
         <v>47</v>
       </c>
       <c r="B50" t="n">
+        <v>3416302</v>
+      </c>
+      <c r="C50" t="n">
         <v>270766</v>
       </c>
     </row>
@@ -833,6 +989,9 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
+        <v>3866563</v>
+      </c>
+      <c r="C51" t="n">
         <v>303258</v>
       </c>
     </row>
@@ -841,6 +1000,9 @@
         <v>49</v>
       </c>
       <c r="B52" t="n">
+        <v>4374577</v>
+      </c>
+      <c r="C52" t="n">
         <v>339649</v>
       </c>
     </row>
@@ -849,6 +1011,9 @@
         <v>50</v>
       </c>
       <c r="B53" t="n">
+        <v>4947619</v>
+      </c>
+      <c r="C53" t="n">
         <v>380407</v>
       </c>
     </row>
@@ -857,6 +1022,9 @@
         <v>51</v>
       </c>
       <c r="B54" t="n">
+        <v>5593868</v>
+      </c>
+      <c r="C54" t="n">
         <v>426056</v>
       </c>
     </row>
@@ -865,6 +1033,9 @@
         <v>52</v>
       </c>
       <c r="B55" t="n">
+        <v>6322519</v>
+      </c>
+      <c r="C55" t="n">
         <v>477183</v>
       </c>
     </row>
@@ -873,6 +1044,9 @@
         <v>53</v>
       </c>
       <c r="B56" t="n">
+        <v>7143905</v>
+      </c>
+      <c r="C56" t="n">
         <v>534445</v>
       </c>
     </row>
@@ -881,6 +1055,9 @@
         <v>54</v>
       </c>
       <c r="B57" t="n">
+        <v>8069639</v>
+      </c>
+      <c r="C57" t="n">
         <v>598578</v>
       </c>
     </row>
@@ -889,6 +1066,9 @@
         <v>55</v>
       </c>
       <c r="B58" t="n">
+        <v>9112799</v>
+      </c>
+      <c r="C58" t="n">
         <v>670408</v>
       </c>
     </row>
@@ -897,6 +1077,9 @@
         <v>56</v>
       </c>
       <c r="B59" t="n">
+        <v>10288038</v>
+      </c>
+      <c r="C59" t="n">
         <v>750857</v>
       </c>
     </row>
@@ -905,6 +1088,9 @@
         <v>57</v>
       </c>
       <c r="B60" t="n">
+        <v>11611837</v>
+      </c>
+      <c r="C60" t="n">
         <v>840959</v>
       </c>
     </row>
@@ -913,6 +1099,9 @@
         <v>58</v>
       </c>
       <c r="B61" t="n">
+        <v>13102745</v>
+      </c>
+      <c r="C61" t="n">
         <v>941874</v>
       </c>
     </row>
@@ -921,6 +1110,9 @@
         <v>59</v>
       </c>
       <c r="B62" t="n">
+        <v>14781567</v>
+      </c>
+      <c r="C62" t="n">
         <v>1054899</v>
       </c>
     </row>
@@ -929,6 +1121,9 @@
         <v>60</v>
       </c>
       <c r="B63" t="n">
+        <v>16671681</v>
+      </c>
+      <c r="C63" t="n">
         <v>1181487</v>
       </c>
     </row>
@@ -937,6 +1132,9 @@
         <v>61</v>
       </c>
       <c r="B64" t="n">
+        <v>18799359</v>
+      </c>
+      <c r="C64" t="n">
         <v>1323266</v>
       </c>
     </row>
@@ -945,6 +1143,9 @@
         <v>62</v>
       </c>
       <c r="B65" t="n">
+        <v>21194085</v>
+      </c>
+      <c r="C65" t="n">
         <v>1482058</v>
       </c>
     </row>
@@ -953,6 +1154,9 @@
         <v>63</v>
       </c>
       <c r="B66" t="n">
+        <v>23888995</v>
+      </c>
+      <c r="C66" t="n">
         <v>1659905</v>
       </c>
     </row>
@@ -961,6 +1165,9 @@
         <v>64</v>
       </c>
       <c r="B67" t="n">
+        <v>26921287</v>
+      </c>
+      <c r="C67" t="n">
         <v>1859093</v>
       </c>
     </row>
@@ -969,6 +1176,9 @@
         <v>65</v>
       </c>
       <c r="B68" t="n">
+        <v>30332755</v>
+      </c>
+      <c r="C68" t="n">
         <v>2082184</v>
       </c>
     </row>
@@ -977,6 +1187,9 @@
         <v>66</v>
       </c>
       <c r="B69" t="n">
+        <v>34170308</v>
+      </c>
+      <c r="C69" t="n">
         <v>2332046</v>
       </c>
     </row>
@@ -985,6 +1198,9 @@
         <v>67</v>
       </c>
       <c r="B70" t="n">
+        <v>38486624</v>
+      </c>
+      <c r="C70" t="n">
         <v>2611892</v>
       </c>
     </row>
@@ -993,6 +1209,9 @@
         <v>68</v>
       </c>
       <c r="B71" t="n">
+        <v>43340827</v>
+      </c>
+      <c r="C71" t="n">
         <v>2925319</v>
       </c>
     </row>
@@ -1001,6 +1220,9 @@
         <v>69</v>
       </c>
       <c r="B72" t="n">
+        <v>48799306</v>
+      </c>
+      <c r="C72" t="n">
         <v>3276357</v>
       </c>
     </row>
@@ -1009,6 +1231,9 @@
         <v>70</v>
       </c>
       <c r="B73" t="n">
+        <v>54936597</v>
+      </c>
+      <c r="C73" t="n">
         <v>3669520</v>
       </c>
     </row>
@@ -1017,6 +1242,9 @@
         <v>71</v>
       </c>
       <c r="B74" t="n">
+        <v>60180017</v>
+      </c>
+      <c r="C74" t="n">
         <v>3999777</v>
       </c>
     </row>
@@ -1025,6 +1253,9 @@
         <v>72</v>
       </c>
       <c r="B75" t="n">
+        <v>65914213</v>
+      </c>
+      <c r="C75" t="n">
         <v>4359757</v>
       </c>
     </row>
@@ -1033,6 +1264,9 @@
         <v>73</v>
       </c>
       <c r="B76" t="n">
+        <v>72184545</v>
+      </c>
+      <c r="C76" t="n">
         <v>4752135</v>
       </c>
     </row>
@@ -1041,6 +1275,9 @@
         <v>74</v>
       </c>
       <c r="B77" t="n">
+        <v>79040534</v>
+      </c>
+      <c r="C77" t="n">
         <v>5179827</v>
       </c>
     </row>
@@ -1049,6 +1286,9 @@
         <v>75</v>
       </c>
       <c r="B78" t="n">
+        <v>86536246</v>
+      </c>
+      <c r="C78" t="n">
         <v>5646012</v>
       </c>
     </row>
@@ -1057,6 +1297,9 @@
         <v>76</v>
       </c>
       <c r="B79" t="n">
+        <v>94730665</v>
+      </c>
+      <c r="C79" t="n">
         <v>6154153</v>
       </c>
     </row>
@@ -1065,6 +1308,9 @@
         <v>77</v>
       </c>
       <c r="B80" t="n">
+        <v>103688195</v>
+      </c>
+      <c r="C80" t="n">
         <v>6708026</v>
       </c>
     </row>
@@ -1073,6 +1319,9 @@
         <v>78</v>
       </c>
       <c r="B81" t="n">
+        <v>113479164</v>
+      </c>
+      <c r="C81" t="n">
         <v>7311749</v>
       </c>
     </row>
@@ -1081,6 +1330,9 @@
         <v>79</v>
       </c>
       <c r="B82" t="n">
+        <v>124180263</v>
+      </c>
+      <c r="C82" t="n">
         <v>7969806</v>
       </c>
     </row>
@@ -1089,6 +1341,9 @@
         <v>80</v>
       </c>
       <c r="B83" t="n">
+        <v>135875260</v>
+      </c>
+      <c r="C83" t="n">
         <v>8687089</v>
       </c>
     </row>
@@ -1097,6 +1352,9 @@
         <v>81</v>
       </c>
       <c r="B84" t="n">
+        <v>148655527</v>
+      </c>
+      <c r="C84" t="n">
         <v>9468927</v>
       </c>
     </row>
@@ -1105,6 +1363,9 @@
         <v>82</v>
       </c>
       <c r="B85" t="n">
+        <v>162620805</v>
+      </c>
+      <c r="C85" t="n">
         <v>10321130</v>
       </c>
     </row>
@@ -1113,6 +1374,9 @@
         <v>83</v>
       </c>
       <c r="B86" t="n">
+        <v>177879956</v>
+      </c>
+      <c r="C86" t="n">
         <v>11250032</v>
       </c>
     </row>
@@ -1121,6 +1385,9 @@
         <v>84</v>
       </c>
       <c r="B87" t="n">
+        <v>194551749</v>
+      </c>
+      <c r="C87" t="n">
         <v>12262535</v>
       </c>
     </row>
@@ -1129,6 +1396,9 @@
         <v>85</v>
       </c>
       <c r="B88" t="n">
+        <v>212765800</v>
+      </c>
+      <c r="C88" t="n">
         <v>13366163</v>
       </c>
     </row>
@@ -1137,6 +1407,9 @@
         <v>86</v>
       </c>
       <c r="B89" t="n">
+        <v>232663547</v>
+      </c>
+      <c r="C89" t="n">
         <v>14569117</v>
       </c>
     </row>
@@ -1145,6 +1418,9 @@
         <v>87</v>
       </c>
       <c r="B90" t="n">
+        <v>254399351</v>
+      </c>
+      <c r="C90" t="n">
         <v>15880338</v>
       </c>
     </row>
@@ -1153,6 +1429,9 @@
         <v>88</v>
       </c>
       <c r="B91" t="n">
+        <v>278141587</v>
+      </c>
+      <c r="C91" t="n">
         <v>17309568</v>
       </c>
     </row>
@@ -1161,6 +1440,9 @@
         <v>89</v>
       </c>
       <c r="B92" t="n">
+        <v>304074036</v>
+      </c>
+      <c r="C92" t="n">
         <v>18867430</v>
       </c>
     </row>
@@ -1169,6 +1451,9 @@
         <v>90</v>
       </c>
       <c r="B93" t="n">
+        <v>332397139</v>
+      </c>
+      <c r="C93" t="n">
         <v>20565498</v>
       </c>
     </row>
@@ -1177,6 +1462,9 @@
         <v>91</v>
       </c>
       <c r="B94" t="n">
+        <v>363329677</v>
+      </c>
+      <c r="C94" t="n">
         <v>22416393</v>
       </c>
     </row>
@@ -1185,6 +1473,9 @@
         <v>92</v>
       </c>
       <c r="B95" t="n">
+        <v>397110280</v>
+      </c>
+      <c r="C95" t="n">
         <v>24433868</v>
       </c>
     </row>
@@ -1193,6 +1484,9 @@
         <v>93</v>
       </c>
       <c r="B96" t="n">
+        <v>433999353</v>
+      </c>
+      <c r="C96" t="n">
         <v>26632917</v>
       </c>
     </row>
@@ -1201,6 +1495,9 @@
         <v>94</v>
       </c>
       <c r="B97" t="n">
+        <v>474280916</v>
+      </c>
+      <c r="C97" t="n">
         <v>29029879</v>
       </c>
     </row>
@@ -1209,6 +1506,9 @@
         <v>95</v>
       </c>
       <c r="B98" t="n">
+        <v>518264896</v>
+      </c>
+      <c r="C98" t="n">
         <v>31642568</v>
       </c>
     </row>
@@ -1217,6 +1517,9 @@
         <v>96</v>
       </c>
       <c r="B99" t="n">
+        <v>566289366</v>
+      </c>
+      <c r="C99" t="n">
         <v>34490399</v>
       </c>
     </row>
@@ -1225,6 +1528,9 @@
         <v>97</v>
       </c>
       <c r="B100" t="n">
+        <v>618723142</v>
+      </c>
+      <c r="C100" t="n">
         <v>37594535</v>
       </c>
     </row>
@@ -1233,6 +1539,9 @@
         <v>98</v>
       </c>
       <c r="B101" t="n">
+        <v>675968551</v>
+      </c>
+      <c r="C101" t="n">
         <v>40978043</v>
       </c>
     </row>
@@ -1241,6 +1550,9 @@
         <v>99</v>
       </c>
       <c r="B102" t="n">
+        <v>738464489</v>
+      </c>
+      <c r="C102" t="n">
         <v>44666067</v>
       </c>
     </row>
@@ -1249,6 +1561,9 @@
         <v>100</v>
       </c>
       <c r="B103" t="n">
+        <v>806689707</v>
+      </c>
+      <c r="C103" t="n">
         <v>48686013</v>
       </c>
     </row>
@@ -1257,6 +1572,9 @@
         <v>101</v>
       </c>
       <c r="B104" t="n">
+        <v>881166458</v>
+      </c>
+      <c r="C104" t="n">
         <v>53067755</v>
       </c>
     </row>
@@ -1265,6 +1583,9 @@
         <v>102</v>
       </c>
       <c r="B105" t="n">
+        <v>962464372</v>
+      </c>
+      <c r="C105" t="n">
         <v>57843853</v>
       </c>
     </row>
@@ -1273,6 +1594,9 @@
         <v>103</v>
       </c>
       <c r="B106" t="n">
+        <v>1051204815</v>
+      </c>
+      <c r="C106" t="n">
         <v>63049799</v>
       </c>
     </row>
@@ -1281,6 +1605,9 @@
         <v>104</v>
       </c>
       <c r="B107" t="n">
+        <v>1148065574</v>
+      </c>
+      <c r="C107" t="n">
         <v>68724281</v>
       </c>
     </row>
@@ -1289,6 +1616,9 @@
         <v>105</v>
       </c>
       <c r="B108" t="n">
+        <v>1253785889</v>
+      </c>
+      <c r="C108" t="n">
         <v>74909466</v>
       </c>
     </row>
@@ -1297,6 +1627,9 @@
         <v>106</v>
       </c>
       <c r="B109" t="n">
+        <v>1369172096</v>
+      </c>
+      <c r="C109" t="n">
         <v>81651318</v>
       </c>
     </row>
@@ -1305,6 +1638,9 @@
         <v>107</v>
       </c>
       <c r="B110" t="n">
+        <v>1495103656</v>
+      </c>
+      <c r="C110" t="n">
         <v>88999937</v>
       </c>
     </row>
@@ -1313,6 +1649,9 @@
         <v>108</v>
       </c>
       <c r="B111" t="n">
+        <v>1632539765</v>
+      </c>
+      <c r="C111" t="n">
         <v>97009931</v>
       </c>
     </row>
@@ -1321,6 +1660,9 @@
         <v>109</v>
       </c>
       <c r="B112" t="n">
+        <v>1782526622</v>
+      </c>
+      <c r="C112" t="n">
         <v>105740825</v>
       </c>
     </row>
@@ -1329,6 +1671,9 @@
         <v>110</v>
       </c>
       <c r="B113" t="n">
+        <v>1946205245</v>
+      </c>
+      <c r="C113" t="n">
         <v>115257500</v>
       </c>
     </row>
@@ -1337,6 +1682,9 @@
         <v>111</v>
       </c>
       <c r="B114" t="n">
+        <v>2085832520</v>
+      </c>
+      <c r="C114" t="n">
         <v>123325525</v>
       </c>
     </row>
@@ -1345,6 +1693,9 @@
         <v>112</v>
       </c>
       <c r="B115" t="n">
+        <v>2235381560</v>
+      </c>
+      <c r="C115" t="n">
         <v>131958311</v>
       </c>
     </row>
@@ -1353,6 +1704,9 @@
         <v>113</v>
       </c>
       <c r="B116" t="n">
+        <v>2395553362</v>
+      </c>
+      <c r="C116" t="n">
         <v>141195393</v>
       </c>
     </row>
@@ -1361,6 +1715,9 @@
         <v>114</v>
       </c>
       <c r="B117" t="n">
+        <v>2567098233</v>
+      </c>
+      <c r="C117" t="n">
         <v>151079071</v>
       </c>
     </row>
@@ -1369,6 +1726,9 @@
         <v>115</v>
       </c>
       <c r="B118" t="n">
+        <v>2750819276</v>
+      </c>
+      <c r="C118" t="n">
         <v>161654605</v>
       </c>
     </row>
@@ -1377,6 +1737,9 @@
         <v>116</v>
       </c>
       <c r="B119" t="n">
+        <v>2947576199</v>
+      </c>
+      <c r="C119" t="n">
         <v>172970428</v>
       </c>
     </row>
@@ -1385,6 +1748,9 @@
         <v>117</v>
       </c>
       <c r="B120" t="n">
+        <v>3158289121</v>
+      </c>
+      <c r="C120" t="n">
         <v>185078358</v>
       </c>
     </row>
@@ -1393,6 +1759,9 @@
         <v>118</v>
       </c>
       <c r="B121" t="n">
+        <v>3383942946</v>
+      </c>
+      <c r="C121" t="n">
         <v>198033843</v>
       </c>
     </row>
@@ -1401,6 +1770,9 @@
         <v>119</v>
       </c>
       <c r="B122" t="n">
+        <v>3625591864</v>
+      </c>
+      <c r="C122" t="n">
         <v>211896212</v>
       </c>
     </row>
@@ -1409,6 +1781,9 @@
         <v>120</v>
       </c>
       <c r="B123" t="n">
+        <v>3884364220</v>
+      </c>
+      <c r="C123" t="n">
         <v>226728947</v>
       </c>
     </row>
@@ -1417,6 +1792,9 @@
         <v>121</v>
       </c>
       <c r="B124" t="n">
+        <v>4161467709</v>
+      </c>
+      <c r="C124" t="n">
         <v>242599973</v>
       </c>
     </row>
@@ -1425,6 +1803,9 @@
         <v>122</v>
       </c>
       <c r="B125" t="n">
+        <v>4458194984</v>
+      </c>
+      <c r="C125" t="n">
         <v>259581971</v>
       </c>
     </row>
@@ -1433,6 +1814,9 @@
         <v>123</v>
       </c>
       <c r="B126" t="n">
+        <v>4775929580</v>
+      </c>
+      <c r="C126" t="n">
         <v>277752709</v>
       </c>
     </row>
@@ -1441,6 +1825,9 @@
         <v>124</v>
       </c>
       <c r="B127" t="n">
+        <v>5116152316</v>
+      </c>
+      <c r="C127" t="n">
         <v>297195399</v>
       </c>
     </row>
@@ -1449,6 +1836,9 @@
         <v>125</v>
       </c>
       <c r="B128" t="n">
+        <v>5480448105</v>
+      </c>
+      <c r="C128" t="n">
         <v>317999077</v>
       </c>
     </row>
@@ -1457,6 +1847,9 @@
         <v>126</v>
       </c>
       <c r="B129" t="n">
+        <v>5870513276</v>
+      </c>
+      <c r="C129" t="n">
         <v>340259012</v>
       </c>
     </row>
@@ -1465,6 +1858,9 @@
         <v>127</v>
       </c>
       <c r="B130" t="n">
+        <v>6288163415</v>
+      </c>
+      <c r="C130" t="n">
         <v>364077143</v>
       </c>
     </row>
@@ -1473,6 +1869,9 @@
         <v>128</v>
       </c>
       <c r="B131" t="n">
+        <v>6735341677</v>
+      </c>
+      <c r="C131" t="n">
         <v>389562543</v>
       </c>
     </row>
@@ -1481,6 +1880,9 @@
         <v>129</v>
       </c>
       <c r="B132" t="n">
+        <v>7214127786</v>
+      </c>
+      <c r="C132" t="n">
         <v>416831921</v>
       </c>
     </row>
@@ -1489,6 +1891,9 @@
         <v>130</v>
       </c>
       <c r="B133" t="n">
+        <v>7726747591</v>
+      </c>
+      <c r="C133" t="n">
         <v>446010155</v>
       </c>
     </row>
@@ -1497,6 +1902,9 @@
         <v>131</v>
       </c>
       <c r="B134" t="n">
+        <v>8275583359</v>
+      </c>
+      <c r="C134" t="n">
         <v>477230866</v>
       </c>
     </row>
@@ -1505,6 +1913,9 @@
         <v>132</v>
       </c>
       <c r="B135" t="n">
+        <v>8863184694</v>
+      </c>
+      <c r="C135" t="n">
         <v>510637027</v>
       </c>
     </row>
@@ -1513,6 +1924,9 @@
         <v>133</v>
       </c>
       <c r="B136" t="n">
+        <v>9492280302</v>
+      </c>
+      <c r="C136" t="n">
         <v>546381619</v>
       </c>
     </row>
@@ -1521,6 +1935,9 @@
         <v>134</v>
       </c>
       <c r="B137" t="n">
+        <v>10165790564</v>
+      </c>
+      <c r="C137" t="n">
         <v>584628332</v>
       </c>
     </row>
@@ -1529,6 +1946,9 @@
         <v>135</v>
       </c>
       <c r="B138" t="n">
+        <v>10886840988</v>
+      </c>
+      <c r="C138" t="n">
         <v>625552315</v>
       </c>
     </row>
@@ -1537,6 +1957,9 @@
         <v>136</v>
       </c>
       <c r="B139" t="n">
+        <v>11658776577</v>
+      </c>
+      <c r="C139" t="n">
         <v>669340977</v>
       </c>
     </row>
@@ -1545,6 +1968,9 @@
         <v>137</v>
       </c>
       <c r="B140" t="n">
+        <v>12485177241</v>
+      </c>
+      <c r="C140" t="n">
         <v>716194846</v>
       </c>
     </row>
@@ -1553,6 +1979,9 @@
         <v>138</v>
       </c>
       <c r="B141" t="n">
+        <v>13369874230</v>
+      </c>
+      <c r="C141" t="n">
         <v>766328485</v>
       </c>
     </row>
@@ -1561,6 +1990,9 @@
         <v>139</v>
       </c>
       <c r="B142" t="n">
+        <v>14316967843</v>
+      </c>
+      <c r="C142" t="n">
         <v>819971479</v>
       </c>
     </row>
@@ -1569,6 +2001,9 @@
         <v>140</v>
       </c>
       <c r="B143" t="n">
+        <v>15330846218</v>
+      </c>
+      <c r="C143" t="n">
         <v>877369482</v>
       </c>
     </row>
@@ -1577,6 +2012,9 @@
         <v>141</v>
       </c>
       <c r="B144" t="n">
+        <v>16416205590</v>
+      </c>
+      <c r="C144" t="n">
         <v>938785346</v>
       </c>
     </row>
@@ -1585,6 +2023,9 @@
         <v>142</v>
       </c>
       <c r="B145" t="n">
+        <v>17578071811</v>
+      </c>
+      <c r="C145" t="n">
         <v>1004500320</v>
       </c>
     </row>
@@ -1593,6 +2034,9 @@
         <v>143</v>
       </c>
       <c r="B146" t="n">
+        <v>18821823556</v>
+      </c>
+      <c r="C146" t="n">
         <v>1074815343</v>
       </c>
     </row>
@@ -1601,6 +2045,9 @@
         <v>144</v>
       </c>
       <c r="B147" t="n">
+        <v>20153216968</v>
+      </c>
+      <c r="C147" t="n">
         <v>1150052417</v>
       </c>
     </row>
@@ -1609,6 +2056,9 @@
         <v>145</v>
       </c>
       <c r="B148" t="n">
+        <v>21578412208</v>
+      </c>
+      <c r="C148" t="n">
         <v>1230556086</v>
       </c>
     </row>
@@ -1617,6 +2067,9 @@
         <v>146</v>
       </c>
       <c r="B149" t="n">
+        <v>23104001746</v>
+      </c>
+      <c r="C149" t="n">
         <v>1316695012</v>
       </c>
     </row>
@@ -1625,6 +2078,9 @@
         <v>147</v>
       </c>
       <c r="B150" t="n">
+        <v>24737040667</v>
+      </c>
+      <c r="C150" t="n">
         <v>1408863663</v>
       </c>
     </row>
@@ -1633,6 +2089,9 @@
         <v>148</v>
       </c>
       <c r="B151" t="n">
+        <v>26485079096</v>
+      </c>
+      <c r="C151" t="n">
         <v>1507484119</v>
       </c>
     </row>
@@ -1641,6 +2100,9 @@
         <v>149</v>
       </c>
       <c r="B152" t="n">
+        <v>28356196941</v>
+      </c>
+      <c r="C152" t="n">
         <v>1613008007</v>
       </c>
     </row>
@@ -1649,6 +2111,9 @@
         <v>150</v>
       </c>
       <c r="B153" t="n">
+        <v>30359041012</v>
+      </c>
+      <c r="C153" t="n">
         <v>1725918568</v>
       </c>
     </row>
@@ -1657,6 +2122,9 @@
         <v>151</v>
       </c>
       <c r="B154" t="n">
+        <v>32502864722</v>
+      </c>
+      <c r="C154" t="n">
         <v>1846732868</v>
       </c>
     </row>
@@ -1665,6 +2133,9 @@
         <v>152</v>
       </c>
       <c r="B155" t="n">
+        <v>34797570650</v>
+      </c>
+      <c r="C155" t="n">
         <v>1976004168</v>
       </c>
     </row>
@@ -1673,6 +2144,9 @@
         <v>153</v>
       </c>
       <c r="B156" t="n">
+        <v>37253756088</v>
+      </c>
+      <c r="C156" t="n">
         <v>2114324460</v>
       </c>
     </row>
@@ -1681,6 +2155,9 @@
         <v>154</v>
       </c>
       <c r="B157" t="n">
+        <v>39882761624</v>
+      </c>
+      <c r="C157" t="n">
         <v>2262327172</v>
       </c>
     </row>
@@ -1689,6 +2166,9 @@
         <v>155</v>
       </c>
       <c r="B158" t="n">
+        <v>42696723337</v>
+      </c>
+      <c r="C158" t="n">
         <v>2420690074</v>
       </c>
     </row>
@@ -1697,6 +2177,9 @@
         <v>156</v>
       </c>
       <c r="B159" t="n">
+        <v>45708628502</v>
+      </c>
+      <c r="C159" t="n">
         <v>2590138379</v>
       </c>
     </row>
@@ -1705,6 +2188,9 @@
         <v>157</v>
       </c>
       <c r="B160" t="n">
+        <v>48932375280</v>
+      </c>
+      <c r="C160" t="n">
         <v>2771448066</v>
       </c>
     </row>
@@ -1713,6 +2199,9 @@
         <v>158</v>
       </c>
       <c r="B161" t="n">
+        <v>52382836513</v>
+      </c>
+      <c r="C161" t="n">
         <v>2965449431</v>
       </c>
     </row>
@@ -1721,6 +2210,9 @@
         <v>159</v>
       </c>
       <c r="B162" t="n">
+        <v>56075928058</v>
+      </c>
+      <c r="C162" t="n">
         <v>3173030891</v>
       </c>
     </row>
@@ -1729,6 +2221,9 @@
         <v>160</v>
       </c>
       <c r="B163" t="n">
+        <v>60028681899</v>
+      </c>
+      <c r="C163" t="n">
         <v>3395143053</v>
       </c>
     </row>
@@ -1737,6 +2232,9 @@
         <v>161</v>
       </c>
       <c r="B164" t="n">
+        <v>63358492697</v>
+      </c>
+      <c r="C164" t="n">
         <v>3581875921</v>
       </c>
     </row>
@@ -1745,6 +2243,9 @@
         <v>162</v>
       </c>
       <c r="B165" t="n">
+        <v>66872260504</v>
+      </c>
+      <c r="C165" t="n">
         <v>3778879097</v>
       </c>
     </row>
@@ -1753,6 +2254,9 @@
         <v>163</v>
       </c>
       <c r="B166" t="n">
+        <v>70580126602</v>
+      </c>
+      <c r="C166" t="n">
         <v>3986717447</v>
       </c>
     </row>
@@ -1761,6 +2265,9 @@
         <v>164</v>
       </c>
       <c r="B167" t="n">
+        <v>74492790774</v>
+      </c>
+      <c r="C167" t="n">
         <v>4205986907</v>
       </c>
     </row>
@@ -1769,6 +2276,9 @@
         <v>165</v>
       </c>
       <c r="B168" t="n">
+        <v>78621541952</v>
+      </c>
+      <c r="C168" t="n">
         <v>4437316187</v>
       </c>
     </row>
@@ -1777,6 +2287,9 @@
         <v>166</v>
       </c>
       <c r="B169" t="n">
+        <v>82978290700</v>
+      </c>
+      <c r="C169" t="n">
         <v>4681368577</v>
       </c>
     </row>
@@ -1785,6 +2298,9 @@
         <v>167</v>
       </c>
       <c r="B170" t="n">
+        <v>87575603428</v>
+      </c>
+      <c r="C170" t="n">
         <v>4938843849</v>
       </c>
     </row>
@@ -1793,6 +2309,9 @@
         <v>168</v>
       </c>
       <c r="B171" t="n">
+        <v>92426738426</v>
+      </c>
+      <c r="C171" t="n">
         <v>5210480260</v>
       </c>
     </row>
@@ -1801,6 +2320,9 @@
         <v>169</v>
       </c>
       <c r="B172" t="n">
+        <v>97545684026</v>
+      </c>
+      <c r="C172" t="n">
         <v>5497056674</v>
       </c>
     </row>
@@ -1809,6 +2331,9 @@
         <v>170</v>
       </c>
       <c r="B173" t="n">
+        <v>102947198727</v>
+      </c>
+      <c r="C173" t="n">
         <v>5799394792</v>
       </c>
     </row>
@@ -1817,6 +2342,9 @@
         <v>171</v>
       </c>
       <c r="B174" t="n">
+        <v>108646853516</v>
+      </c>
+      <c r="C174" t="n">
         <v>6118361505</v>
       </c>
     </row>
@@ -1825,6 +2353,9 @@
         <v>172</v>
       </c>
       <c r="B175" t="n">
+        <v>114661076735</v>
+      </c>
+      <c r="C175" t="n">
         <v>6454871388</v>
       </c>
     </row>
@@ -1833,6 +2364,9 @@
         <v>173</v>
       </c>
       <c r="B176" t="n">
+        <v>121007201107</v>
+      </c>
+      <c r="C176" t="n">
         <v>6809889314</v>
       </c>
     </row>
@@ -1841,6 +2375,9 @@
         <v>174</v>
       </c>
       <c r="B177" t="n">
+        <v>127703513617</v>
+      </c>
+      <c r="C177" t="n">
         <v>7184433227</v>
       </c>
     </row>
@@ -1849,6 +2386,9 @@
         <v>175</v>
       </c>
       <c r="B178" t="n">
+        <v>134769307904</v>
+      </c>
+      <c r="C178" t="n">
         <v>7579577054</v>
       </c>
     </row>
@@ -1857,6 +2397,9 @@
         <v>176</v>
       </c>
       <c r="B179" t="n">
+        <v>142224939794</v>
+      </c>
+      <c r="C179" t="n">
         <v>7996453792</v>
       </c>
     </row>
@@ -1865,6 +2408,9 @@
         <v>177</v>
       </c>
       <c r="B180" t="n">
+        <v>150091885643</v>
+      </c>
+      <c r="C180" t="n">
         <v>8436258751</v>
       </c>
     </row>
@@ -1873,6 +2419,9 @@
         <v>178</v>
       </c>
       <c r="B181" t="n">
+        <v>158392804009</v>
+      </c>
+      <c r="C181" t="n">
         <v>8900252982</v>
       </c>
     </row>
@@ -1881,6 +2430,9 @@
         <v>179</v>
       </c>
       <c r="B182" t="n">
+        <v>167151600762</v>
+      </c>
+      <c r="C182" t="n">
         <v>9389766896</v>
       </c>
     </row>
@@ -1889,6 +2441,9 @@
         <v>180</v>
       </c>
       <c r="B183" t="n">
+        <v>176393497648</v>
+      </c>
+      <c r="C183" t="n">
         <v>9906204075</v>
       </c>
     </row>
@@ -1897,6 +2452,9 @@
         <v>181</v>
       </c>
       <c r="B184" t="n">
+        <v>186145104739</v>
+      </c>
+      <c r="C184" t="n">
         <v>10451045299</v>
       </c>
     </row>
@@ -1905,6 +2463,9 @@
         <v>182</v>
       </c>
       <c r="B185" t="n">
+        <v>196434496809</v>
+      </c>
+      <c r="C185" t="n">
         <v>11025852791</v>
       </c>
     </row>
@@ -1913,6 +2474,9 @@
         <v>183</v>
       </c>
       <c r="B186" t="n">
+        <v>207291293882</v>
+      </c>
+      <c r="C186" t="n">
         <v>11632274694</v>
       </c>
     </row>
@@ -1921,6 +2485,9 @@
         <v>184</v>
       </c>
       <c r="B187" t="n">
+        <v>218746746351</v>
+      </c>
+      <c r="C187" t="n">
         <v>12272049802</v>
       </c>
     </row>
@@ -1929,6 +2496,9 @@
         <v>185</v>
       </c>
       <c r="B188" t="n">
+        <v>230833824599</v>
+      </c>
+      <c r="C188" t="n">
         <v>12947012541</v>
       </c>
     </row>
@@ -1937,6 +2507,9 @@
         <v>186</v>
       </c>
       <c r="B189" t="n">
+        <v>243587313676</v>
+      </c>
+      <c r="C189" t="n">
         <v>13659098231</v>
       </c>
     </row>
@@ -1945,6 +2518,9 @@
         <v>187</v>
       </c>
       <c r="B190" t="n">
+        <v>257043913118</v>
+      </c>
+      <c r="C190" t="n">
         <v>14410348634</v>
       </c>
     </row>
@@ -1953,6 +2529,9 @@
         <v>188</v>
       </c>
       <c r="B191" t="n">
+        <v>271242342295</v>
+      </c>
+      <c r="C191" t="n">
         <v>15202917809</v>
       </c>
     </row>
@@ -1961,6 +2540,9 @@
         <v>189</v>
       </c>
       <c r="B192" t="n">
+        <v>286223451539</v>
+      </c>
+      <c r="C192" t="n">
         <v>16039078288</v>
       </c>
     </row>
@@ -1969,6 +2551,9 @@
         <v>190</v>
       </c>
       <c r="B193" t="n">
+        <v>302030339419</v>
+      </c>
+      <c r="C193" t="n">
         <v>16921227594</v>
       </c>
     </row>
@@ -1977,6 +2562,9 @@
         <v>191</v>
       </c>
       <c r="B194" t="n">
+        <v>318708476376</v>
+      </c>
+      <c r="C194" t="n">
         <v>17851895112</v>
       </c>
     </row>
@@ -1985,6 +2573,9 @@
         <v>192</v>
       </c>
       <c r="B195" t="n">
+        <v>336305835243</v>
+      </c>
+      <c r="C195" t="n">
         <v>18833749343</v>
       </c>
     </row>
@@ -1993,6 +2584,9 @@
         <v>193</v>
       </c>
       <c r="B196" t="n">
+        <v>354873028955</v>
+      </c>
+      <c r="C196" t="n">
         <v>19869605557</v>
       </c>
     </row>
@@ -2001,6 +2595,9 @@
         <v>194</v>
       </c>
       <c r="B197" t="n">
+        <v>374463455737</v>
+      </c>
+      <c r="C197" t="n">
         <v>20962433862</v>
       </c>
     </row>
@@ -2009,6 +2606,9 @@
         <v>195</v>
       </c>
       <c r="B198" t="n">
+        <v>395133452431</v>
+      </c>
+      <c r="C198" t="n">
         <v>22115367725</v>
       </c>
     </row>
@@ -2017,6 +2617,9 @@
         <v>196</v>
       </c>
       <c r="B199" t="n">
+        <v>416942456047</v>
+      </c>
+      <c r="C199" t="n">
         <v>23331712950</v>
       </c>
     </row>
@@ -2025,6 +2628,9 @@
         <v>197</v>
       </c>
       <c r="B200" t="n">
+        <v>439953174420</v>
+      </c>
+      <c r="C200" t="n">
         <v>24614957162</v>
       </c>
     </row>
@@ -2033,6 +2639,9 @@
         <v>198</v>
       </c>
       <c r="B201" t="n">
+        <v>464231766136</v>
+      </c>
+      <c r="C201" t="n">
         <v>25968779806</v>
       </c>
     </row>
@@ -2041,6 +2650,9 @@
         <v>199</v>
       </c>
       <c r="B202" t="n">
+        <v>489848030335</v>
+      </c>
+      <c r="C202" t="n">
         <v>27397062695</v>
       </c>
     </row>
@@ -2049,6 +2661,9 @@
         <v>200</v>
       </c>
       <c r="B203" t="n">
+        <v>516875607050</v>
+      </c>
+      <c r="C203" t="n">
         <v>28903901143</v>
       </c>
     </row>
@@ -2057,6 +2672,9 @@
         <v>201</v>
       </c>
       <c r="B204" t="n">
+        <v>545392188479</v>
+      </c>
+      <c r="C204" t="n">
         <v>30493615706</v>
       </c>
     </row>
@@ -2065,6 +2683,9 @@
         <v>202</v>
       </c>
       <c r="B205" t="n">
+        <v>575479741906</v>
+      </c>
+      <c r="C205" t="n">
         <v>32170764570</v>
       </c>
     </row>
@@ -2073,6 +2694,9 @@
         <v>203</v>
       </c>
       <c r="B206" t="n">
+        <v>607224744919</v>
+      </c>
+      <c r="C206" t="n">
         <v>33940156622</v>
       </c>
     </row>
@@ -2081,6 +2705,9 @@
         <v>204</v>
       </c>
       <c r="B207" t="n">
+        <v>640718433483</v>
+      </c>
+      <c r="C207" t="n">
         <v>35806865236</v>
       </c>
     </row>
@@ -2089,6 +2716,9 @@
         <v>205</v>
       </c>
       <c r="B208" t="n">
+        <v>676057063794</v>
+      </c>
+      <c r="C208" t="n">
         <v>37776242824</v>
       </c>
     </row>
@@ -2097,6 +2727,9 @@
         <v>206</v>
       </c>
       <c r="B209" t="n">
+        <v>713342188382</v>
+      </c>
+      <c r="C209" t="n">
         <v>39853936179</v>
       </c>
     </row>
@@ -2105,6 +2738,9 @@
         <v>207</v>
       </c>
       <c r="B210" t="n">
+        <v>752680947528</v>
+      </c>
+      <c r="C210" t="n">
         <v>42045902669</v>
       </c>
     </row>
@@ -2113,6 +2749,9 @@
         <v>208</v>
       </c>
       <c r="B211" t="n">
+        <v>794186376611</v>
+      </c>
+      <c r="C211" t="n">
         <v>44358427316</v>
       </c>
     </row>
@@ -2121,6 +2760,9 @@
         <v>209</v>
       </c>
       <c r="B212" t="n">
+        <v>837977730428</v>
+      </c>
+      <c r="C212" t="n">
         <v>46798140818</v>
       </c>
     </row>
@@ -2129,6 +2771,9 @@
         <v>210</v>
       </c>
       <c r="B213" t="n">
+        <v>884180825364</v>
+      </c>
+      <c r="C213" t="n">
         <v>49372038563</v>
       </c>
     </row>
@@ -2137,6 +2782,9 @@
         <v>211</v>
       </c>
       <c r="B214" t="n">
+        <v>924085477070</v>
+      </c>
+      <c r="C214" t="n">
         <v>51593780298</v>
       </c>
     </row>
@@ -2145,6 +2793,9 @@
         <v>212</v>
       </c>
       <c r="B215" t="n">
+        <v>965788075067</v>
+      </c>
+      <c r="C215" t="n">
         <v>53915500412</v>
       </c>
     </row>
@@ -2153,6 +2804,9 @@
         <v>213</v>
       </c>
       <c r="B216" t="n">
+        <v>1009369569846</v>
+      </c>
+      <c r="C216" t="n">
         <v>56341697930</v>
       </c>
     </row>
@@ -2161,6 +2815,9 @@
         <v>214</v>
       </c>
       <c r="B217" t="n">
+        <v>1054914555568</v>
+      </c>
+      <c r="C217" t="n">
         <v>58877074337</v>
       </c>
     </row>
@@ -2169,6 +2826,9 @@
         <v>215</v>
       </c>
       <c r="B218" t="n">
+        <v>1102511433919</v>
+      </c>
+      <c r="C218" t="n">
         <v>61526542682</v>
       </c>
     </row>
@@ -2177,6 +2837,9 @@
         <v>216</v>
       </c>
       <c r="B219" t="n">
+        <v>1152252585548</v>
+      </c>
+      <c r="C219" t="n">
         <v>64295237103</v>
       </c>
     </row>
@@ -2185,6 +2848,9 @@
         <v>217</v>
       </c>
       <c r="B220" t="n">
+        <v>1204234549088</v>
+      </c>
+      <c r="C220" t="n">
         <v>67188522773</v>
       </c>
     </row>
@@ -2193,6 +2859,9 @@
         <v>218</v>
       </c>
       <c r="B221" t="n">
+        <v>1258558208283</v>
+      </c>
+      <c r="C221" t="n">
         <v>70212006297</v>
       </c>
     </row>
@@ -2201,6 +2870,9 @@
         <v>219</v>
       </c>
       <c r="B222" t="n">
+        <v>1315328987622</v>
+      </c>
+      <c r="C222" t="n">
         <v>73371546581</v>
       </c>
     </row>
@@ -2209,6 +2881,9 @@
         <v>220</v>
       </c>
       <c r="B223" t="n">
+        <v>1374657056534</v>
+      </c>
+      <c r="C223" t="n">
         <v>76673266177</v>
       </c>
     </row>
@@ -2217,6 +2892,9 @@
         <v>221</v>
       </c>
       <c r="B224" t="n">
+        <v>1436657543069</v>
+      </c>
+      <c r="C224" t="n">
         <v>80123563155</v>
       </c>
     </row>
@@ -2225,6 +2903,9 @@
         <v>222</v>
       </c>
       <c r="B225" t="n">
+        <v>1501450756983</v>
+      </c>
+      <c r="C225" t="n">
         <v>83729123497</v>
       </c>
     </row>
@@ -2233,6 +2914,9 @@
         <v>223</v>
       </c>
       <c r="B226" t="n">
+        <v>1569162422941</v>
+      </c>
+      <c r="C226" t="n">
         <v>87496934054</v>
       </c>
     </row>
@@ -2241,6 +2925,9 @@
         <v>224</v>
       </c>
       <c r="B227" t="n">
+        <v>1639923924249</v>
+      </c>
+      <c r="C227" t="n">
         <v>91434296087</v>
       </c>
     </row>
@@ -2249,6 +2936,9 @@
         <v>225</v>
       </c>
       <c r="B228" t="n">
+        <v>1713872557411</v>
+      </c>
+      <c r="C228" t="n">
         <v>95548839410</v>
       </c>
     </row>
@@ -2257,6 +2947,9 @@
         <v>226</v>
       </c>
       <c r="B229" t="n">
+        <v>1791151798404</v>
+      </c>
+      <c r="C229" t="n">
         <v>99848537184</v>
       </c>
     </row>
@@ -2265,6 +2958,9 @@
         <v>227</v>
       </c>
       <c r="B230" t="n">
+        <v>1871911580588</v>
+      </c>
+      <c r="C230" t="n">
         <v>104341721357</v>
       </c>
     </row>
@@ -2273,6 +2969,9 @@
         <v>228</v>
       </c>
       <c r="B231" t="n">
+        <v>1956308585457</v>
+      </c>
+      <c r="C231" t="n">
         <v>109037098818</v>
       </c>
     </row>
@@ -2281,6 +2980,9 @@
         <v>229</v>
       </c>
       <c r="B232" t="n">
+        <v>2044506546254</v>
+      </c>
+      <c r="C232" t="n">
         <v>113943768265</v>
       </c>
     </row>
@@ -2289,6 +2991,9 @@
         <v>230</v>
       </c>
       <c r="B233" t="n">
+        <v>2136676565327</v>
+      </c>
+      <c r="C233" t="n">
         <v>119071237837</v>
       </c>
     </row>
@@ -2297,6 +3002,9 @@
         <v>231</v>
       </c>
       <c r="B234" t="n">
+        <v>2232997445782</v>
+      </c>
+      <c r="C234" t="n">
         <v>124429443540</v>
       </c>
     </row>
@@ -2305,6 +3013,9 @@
         <v>232</v>
       </c>
       <c r="B235" t="n">
+        <v>2333656038004</v>
+      </c>
+      <c r="C235" t="n">
         <v>130028768499</v>
       </c>
     </row>
@@ -2313,6 +3024,9 @@
         <v>233</v>
       </c>
       <c r="B236" t="n">
+        <v>2438847601852</v>
+      </c>
+      <c r="C236" t="n">
         <v>135880063081</v>
       </c>
     </row>
@@ -2321,6 +3035,9 @@
         <v>234</v>
       </c>
       <c r="B237" t="n">
+        <v>2548776185095</v>
+      </c>
+      <c r="C237" t="n">
         <v>141994665920</v>
       </c>
     </row>
@@ -2329,6 +3046,9 @@
         <v>235</v>
       </c>
       <c r="B238" t="n">
+        <v>2663655018852</v>
+      </c>
+      <c r="C238" t="n">
         <v>148384425887</v>
       </c>
     </row>
@@ -2337,6 +3057,9 @@
         <v>236</v>
       </c>
       <c r="B239" t="n">
+        <v>2783706930875</v>
+      </c>
+      <c r="C239" t="n">
         <v>155061725051</v>
       </c>
     </row>
@@ -2345,6 +3068,9 @@
         <v>237</v>
       </c>
       <c r="B240" t="n">
+        <v>2909164777529</v>
+      </c>
+      <c r="C240" t="n">
         <v>162039502679</v>
       </c>
     </row>
@@ -2353,6 +3079,9 @@
         <v>238</v>
       </c>
       <c r="B241" t="n">
+        <v>3040271894909</v>
+      </c>
+      <c r="C241" t="n">
         <v>169331280299</v>
       </c>
     </row>
@@ -2361,6 +3090,9 @@
         <v>239</v>
       </c>
       <c r="B242" t="n">
+        <v>3177282570655</v>
+      </c>
+      <c r="C242" t="n">
         <v>176951187913</v>
       </c>
     </row>
@@ -2369,6 +3101,9 @@
         <v>240</v>
       </c>
       <c r="B243" t="n">
+        <v>3320462536628</v>
+      </c>
+      <c r="C243" t="n">
         <v>184913991369</v>
       </c>
     </row>
@@ -2377,6 +3112,9 @@
         <v>241</v>
       </c>
       <c r="B244" t="n">
+        <v>3470089484035</v>
+      </c>
+      <c r="C244" t="n">
         <v>193235120980</v>
       </c>
     </row>
@@ -2385,6 +3123,9 @@
         <v>242</v>
       </c>
       <c r="B245" t="n">
+        <v>3626453601627</v>
+      </c>
+      <c r="C245" t="n">
         <v>201930701425</v>
       </c>
     </row>
@@ -2393,6 +3134,9 @@
         <v>243</v>
       </c>
       <c r="B246" t="n">
+        <v>3789858137994</v>
+      </c>
+      <c r="C246" t="n">
         <v>211017582989</v>
       </c>
     </row>
@@ -2401,6 +3145,9 @@
         <v>244</v>
       </c>
       <c r="B247" t="n">
+        <v>3960619989434</v>
+      </c>
+      <c r="C247" t="n">
         <v>220513374223</v>
       </c>
     </row>
@@ -2409,6 +3156,9 @@
         <v>245</v>
       </c>
       <c r="B248" t="n">
+        <v>4139070314064</v>
+      </c>
+      <c r="C248" t="n">
         <v>230436476063</v>
       </c>
     </row>
@@ -2417,6 +3167,9 @@
         <v>246</v>
       </c>
       <c r="B249" t="n">
+        <v>4325555173614</v>
+      </c>
+      <c r="C249" t="n">
         <v>240806117486</v>
       </c>
     </row>
@@ -2425,6 +3178,9 @@
         <v>247</v>
       </c>
       <c r="B250" t="n">
+        <v>4520436204136</v>
+      </c>
+      <c r="C250" t="n">
         <v>251642392773</v>
       </c>
     </row>
@@ -2433,6 +3189,9 @@
         <v>248</v>
       </c>
       <c r="B251" t="n">
+        <v>4724091316885</v>
+      </c>
+      <c r="C251" t="n">
         <v>262966300448</v>
       </c>
     </row>
@@ -2441,6 +3200,9 @@
         <v>249</v>
       </c>
       <c r="B252" t="n">
+        <v>4936915430717</v>
+      </c>
+      <c r="C252" t="n">
         <v>274799783968</v>
       </c>
     </row>
@@ -2449,6 +3211,9 @@
         <v>250</v>
       </c>
       <c r="B253" t="n">
+        <v>5159321237477</v>
+      </c>
+      <c r="C253" t="n">
         <v>287165774246</v>
       </c>
     </row>
@@ -2457,6 +3222,9 @@
         <v>251</v>
       </c>
       <c r="B254" t="n">
+        <v>5391740001830</v>
+      </c>
+      <c r="C254" t="n">
         <v>300088234087</v>
       </c>
     </row>
@@ -2465,6 +3233,9 @@
         <v>252</v>
       </c>
       <c r="B255" t="n">
+        <v>5634622397022</v>
+      </c>
+      <c r="C255" t="n">
         <v>313592204621</v>
       </c>
     </row>
@@ -2473,6 +3244,9 @@
         <v>253</v>
       </c>
       <c r="B256" t="n">
+        <v>5888439378334</v>
+      </c>
+      <c r="C256" t="n">
         <v>327703853829</v>
       </c>
     </row>
@@ -2481,6 +3255,9 @@
         <v>254</v>
       </c>
       <c r="B257" t="n">
+        <v>6153683095811</v>
+      </c>
+      <c r="C257" t="n">
         <v>342450527252</v>
       </c>
     </row>
@@ -2489,6 +3266,9 @@
         <v>255</v>
       </c>
       <c r="B258" t="n">
+        <v>6430867848006</v>
+      </c>
+      <c r="C258" t="n">
         <v>357860800978</v>
       </c>
     </row>
@@ -2497,6 +3277,9 @@
         <v>256</v>
       </c>
       <c r="B259" t="n">
+        <v>6720531078797</v>
+      </c>
+      <c r="C259" t="n">
         <v>373964537022</v>
       </c>
     </row>
@@ -2505,6 +3288,9 @@
         <v>257</v>
       </c>
       <c r="B260" t="n">
+        <v>7023234418870</v>
+      </c>
+      <c r="C260" t="n">
         <v>390792941188</v>
       </c>
     </row>
@@ -2513,6 +3299,9 @@
         <v>258</v>
       </c>
       <c r="B261" t="n">
+        <v>7339564774197</v>
+      </c>
+      <c r="C261" t="n">
         <v>408378623541</v>
       </c>
     </row>
@@ -2521,6 +3310,9 @@
         <v>259</v>
       </c>
       <c r="B262" t="n">
+        <v>7670135463494</v>
+      </c>
+      <c r="C262" t="n">
         <v>426755661601</v>
       </c>
     </row>
@@ -2529,6 +3321,9 @@
         <v>260</v>
       </c>
       <c r="B263" t="n">
+        <v>8015587406733</v>
+      </c>
+      <c r="C263" t="n">
         <v>445959666373</v>
       </c>
     </row>
@@ -2537,6 +3332,9 @@
         <v>261</v>
       </c>
       <c r="B264" t="n">
+        <v>8296431607854</v>
+      </c>
+      <c r="C264" t="n">
         <v>461568254696</v>
       </c>
     </row>
@@ -2545,6 +3343,9 @@
         <v>262</v>
       </c>
       <c r="B265" t="n">
+        <v>8587108176908</v>
+      </c>
+      <c r="C265" t="n">
         <v>477723143610</v>
       </c>
     </row>
@@ -2553,6 +3354,9 @@
         <v>263</v>
       </c>
       <c r="B266" t="n">
+        <v>8887961273442</v>
+      </c>
+      <c r="C266" t="n">
         <v>494443453637</v>
       </c>
     </row>
@@ -2561,6 +3365,9 @@
         <v>264</v>
       </c>
       <c r="B267" t="n">
+        <v>9199347102780</v>
+      </c>
+      <c r="C267" t="n">
         <v>511748974514</v>
       </c>
     </row>
@@ -2569,6 +3376,9 @@
         <v>265</v>
       </c>
       <c r="B268" t="n">
+        <v>9521634337743</v>
+      </c>
+      <c r="C268" t="n">
         <v>529660188622</v>
       </c>
     </row>
@@ -2577,6 +3387,9 @@
         <v>266</v>
       </c>
       <c r="B269" t="n">
+        <v>9855204554935</v>
+      </c>
+      <c r="C269" t="n">
         <v>548198295224</v>
       </c>
     </row>
@@ -2585,6 +3398,9 @@
         <v>267</v>
       </c>
       <c r="B270" t="n">
+        <v>10200452686377</v>
+      </c>
+      <c r="C270" t="n">
         <v>567385235556</v>
       </c>
     </row>
@@ -2593,6 +3409,9 @@
         <v>268</v>
       </c>
       <c r="B271" t="n">
+        <v>10557787487040</v>
+      </c>
+      <c r="C271" t="n">
         <v>587243718801</v>
       </c>
     </row>
@@ -2601,6 +3420,9 @@
         <v>269</v>
       </c>
       <c r="B272" t="n">
+        <v>10927632018503</v>
+      </c>
+      <c r="C272" t="n">
         <v>607797248959</v>
       </c>
     </row>
@@ -2609,6 +3431,9 @@
         <v>270</v>
       </c>
       <c r="B273" t="n">
+        <v>11310424149822</v>
+      </c>
+      <c r="C273" t="n">
         <v>629070152673</v>
       </c>
     </row>
@@ -2617,6 +3442,9 @@
         <v>271</v>
       </c>
       <c r="B274" t="n">
+        <v>11706617075691</v>
+      </c>
+      <c r="C274" t="n">
         <v>651087608016</v>
       </c>
     </row>
@@ -2625,6 +3453,9 @@
         <v>272</v>
       </c>
       <c r="B275" t="n">
+        <v>12116679852954</v>
+      </c>
+      <c r="C275" t="n">
         <v>673875674297</v>
       </c>
     </row>
@@ -2633,6 +3464,9 @@
         <v>273</v>
       </c>
       <c r="B276" t="n">
+        <v>12541097955650</v>
+      </c>
+      <c r="C276" t="n">
         <v>697461322897</v>
       </c>
     </row>
@@ -2641,6 +3475,9 @@
         <v>274</v>
       </c>
       <c r="B277" t="n">
+        <v>12980373849730</v>
+      </c>
+      <c r="C277" t="n">
         <v>721872469198</v>
       </c>
     </row>
@@ -2649,6 +3486,9 @@
         <v>275</v>
       </c>
       <c r="B278" t="n">
+        <v>13435027587731</v>
+      </c>
+      <c r="C278" t="n">
         <v>747138005620</v>
       </c>
     </row>
@@ -2657,6 +3497,9 @@
         <v>276</v>
       </c>
       <c r="B279" t="n">
+        <v>13905597424295</v>
+      </c>
+      <c r="C279" t="n">
         <v>773287835817</v>
       </c>
     </row>
@@ -2665,6 +3508,9 @@
         <v>277</v>
       </c>
       <c r="B280" t="n">
+        <v>14392640453263</v>
+      </c>
+      <c r="C280" t="n">
         <v>800352910071</v>
       </c>
     </row>
@@ -2673,6 +3519,9 @@
         <v>278</v>
       </c>
       <c r="B281" t="n">
+        <v>14896733267033</v>
+      </c>
+      <c r="C281" t="n">
         <v>828365261923</v>
       </c>
     </row>
@@ -2681,6 +3530,9 @@
         <v>279</v>
       </c>
       <c r="B282" t="n">
+        <v>15418472639061</v>
+      </c>
+      <c r="C282" t="n">
         <v>857358046090</v>
       </c>
     </row>
@@ -2689,6 +3541,9 @@
         <v>280</v>
       </c>
       <c r="B283" t="n">
+        <v>15958476230169</v>
+      </c>
+      <c r="C283" t="n">
         <v>887365577704</v>
       </c>
     </row>
@@ -2697,6 +3552,9 @@
         <v>281</v>
       </c>
       <c r="B284" t="n">
+        <v>16517383319535</v>
+      </c>
+      <c r="C284" t="n">
         <v>918423372923</v>
       </c>
     </row>
@@ -2705,6 +3563,9 @@
         <v>282</v>
       </c>
       <c r="B285" t="n">
+        <v>17095855561506</v>
+      </c>
+      <c r="C285" t="n">
         <v>950568190976</v>
       </c>
     </row>
@@ -2713,6 +3574,9 @@
         <v>283</v>
       </c>
       <c r="B286" t="n">
+        <v>17694577768541</v>
+      </c>
+      <c r="C286" t="n">
         <v>983838077660</v>
       </c>
     </row>
@@ -2721,6 +3585,9 @@
         <v>284</v>
       </c>
       <c r="B287" t="n">
+        <v>18314258721896</v>
+      </c>
+      <c r="C287" t="n">
         <v>1018272410378</v>
       </c>
     </row>
@@ -2729,6 +3596,9 @@
         <v>285</v>
       </c>
       <c r="B288" t="n">
+        <v>18955632010455</v>
+      </c>
+      <c r="C288" t="n">
         <v>1053911944741</v>
       </c>
     </row>
@@ -2737,6 +3607,9 @@
         <v>286</v>
       </c>
       <c r="B289" t="n">
+        <v>19619456899037</v>
+      </c>
+      <c r="C289" t="n">
         <v>1090798862807</v>
       </c>
     </row>
@@ -2745,6 +3618,9 @@
         <v>287</v>
       </c>
       <c r="B290" t="n">
+        <v>20306519227021</v>
+      </c>
+      <c r="C290" t="n">
         <v>1128976823005</v>
       </c>
     </row>
@@ -2753,6 +3629,9 @@
         <v>288</v>
       </c>
       <c r="B291" t="n">
+        <v>21017632338498</v>
+      </c>
+      <c r="C291" t="n">
         <v>1168491011810</v>
       </c>
     </row>
@@ -2761,6 +3640,9 @@
         <v>289</v>
       </c>
       <c r="B292" t="n">
+        <v>21753638044929</v>
+      </c>
+      <c r="C292" t="n">
         <v>1209388197224</v>
       </c>
     </row>
@@ -2769,6 +3651,9 @@
         <v>290</v>
       </c>
       <c r="B293" t="n">
+        <v>22515407621458</v>
+      </c>
+      <c r="C293" t="n">
         <v>1251716784127</v>
       </c>
     </row>
@@ -2777,6 +3662,9 @@
         <v>291</v>
       </c>
       <c r="B294" t="n">
+        <v>23303842838206</v>
+      </c>
+      <c r="C294" t="n">
         <v>1295526871571</v>
       </c>
     </row>
@@ -2785,6 +3673,9 @@
         <v>292</v>
       </c>
       <c r="B295" t="n">
+        <v>24119877027596</v>
+      </c>
+      <c r="C295" t="n">
         <v>1340870312076</v>
       </c>
     </row>
@@ -2793,6 +3684,9 @@
         <v>293</v>
       </c>
       <c r="B296" t="n">
+        <v>24964476188997</v>
+      </c>
+      <c r="C296" t="n">
         <v>1387800772999</v>
       </c>
     </row>
@@ -2801,6 +3695,9 @@
         <v>294</v>
       </c>
       <c r="B297" t="n">
+        <v>25838640132079</v>
+      </c>
+      <c r="C297" t="n">
         <v>1436373800054</v>
       </c>
     </row>
@@ -2809,6 +3706,9 @@
         <v>295</v>
       </c>
       <c r="B298" t="n">
+        <v>26743403660187</v>
+      </c>
+      <c r="C298" t="n">
         <v>1486646883055</v>
       </c>
     </row>
@@ -2817,6 +3717,9 @@
         <v>296</v>
       </c>
       <c r="B299" t="n">
+        <v>27679837795170</v>
+      </c>
+      <c r="C299" t="n">
         <v>1538679523962</v>
       </c>
     </row>
@@ -2825,6 +3728,9 @@
         <v>297</v>
       </c>
       <c r="B300" t="n">
+        <v>28649051044936</v>
+      </c>
+      <c r="C300" t="n">
         <v>1592533307301</v>
       </c>
     </row>
@@ -2833,6 +3739,9 @@
         <v>298</v>
       </c>
       <c r="B301" t="n">
+        <v>29652190715530</v>
+      </c>
+      <c r="C301" t="n">
         <v>1648271973057</v>
       </c>
     </row>
@@ -2841,6 +3750,9 @@
         <v>299</v>
       </c>
       <c r="B302" t="n">
+        <v>30690444269047</v>
+      </c>
+      <c r="C302" t="n">
         <v>1705961492114</v>
       </c>
     </row>
@@ -2849,6 +3761,9 @@
         <v>300</v>
       </c>
       <c r="B303" t="n">
+        <v>31765040729128</v>
+      </c>
+      <c r="C303" t="n">
         <v>1765670144338</v>
       </c>
     </row>
